--- a/data/trans_orig/IP19C05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51101</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100989</t>
+          <t>100392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49498</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83899</t>
+          <t>85163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94928</t>
+          <t>95160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90424</t>
+          <t>90849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188619</t>
+          <t>187693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193688</t>
+          <t>193695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>49774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119740</t>
+          <t>120777</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>32769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71841</t>
+          <t>71862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>317461</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>322501</t>
+          <t>322499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>334671</t>
+          <t>334923</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>341003</t>
+          <t>341005</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>654412</t>
+          <t>654697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662606</t>
+          <t>662685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41619</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37614</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82392</t>
+          <t>81866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88375</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42758</t>
+          <t>43374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49078</t>
+          <t>48653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95156</t>
+          <t>94720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100127</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37415</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>80796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90625</t>
+          <t>91228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>94037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182408</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188426</t>
+          <t>188433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>76471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73029</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147075</t>
+          <t>146800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154505</t>
+          <t>153972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>321265</t>
+          <t>321857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>331776</t>
+          <t>332113</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331118</t>
+          <t>331866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>340077</t>
+          <t>340072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>656693</t>
+          <t>657123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>670125</t>
+          <t>670298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>45267</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87996</t>
+          <t>88616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49778</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>49717</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102302</t>
+          <t>101668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108683</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>61775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103286</t>
+          <t>103463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98107</t>
+          <t>98424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>204775</t>
+          <t>205220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212843</t>
+          <t>212969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62972</t>
+          <t>62072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68959</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134517</t>
+          <t>135415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141467</t>
+          <t>141890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>327426</t>
+          <t>327919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>338085</t>
+          <t>337973</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337715</t>
+          <t>338213</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346140</t>
+          <t>346273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>669922</t>
+          <t>669163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>682377</t>
+          <t>682761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C05-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3119</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3582</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54163</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51676</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51213</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>152</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100392</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40498</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3683</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3216</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52727</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>49741</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>131</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5305</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94603</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91218</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>97539</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95160</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95513</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94603</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>90849</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>289</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187693</t>
+          <t>188453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193695</t>
+          <t>193693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4358</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>53785</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>49774</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>50297</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,02%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120777</t>
+          <t>120335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3931</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2958</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>35083</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31796</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>35083</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>32769</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>113</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71862</t>
+          <t>72476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2103</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6316</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5673</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2837</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>338851</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>334359</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>340996</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>320995</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>316782</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>322499</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>317425</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>322502</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>338851</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>334923</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>341005</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>654697</t>
+          <t>655316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662685</t>
+          <t>662855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3053</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2371</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6712</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5960</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3598</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40227</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37831</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45867</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41526</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>47558</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42278</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>47569</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40227</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37286</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81866</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88372</t>
+          <t>88198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1202</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4121</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52268</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49230</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>46293</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43374</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43472</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>52268</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48653</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>142</t>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>95363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100128</t>
+          <t>100127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,67 +4048,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1433</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5070</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35251</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40292</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36655</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37422</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38403</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34787</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>116</t>
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75146</t>
+          <t>74845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80796</t>
+          <t>80799</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3924</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5734</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>97187</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>94042</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89225</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85494</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91228</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85790</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90620</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>97187</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>94037</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>182424</t>
+          <t>182555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188433</t>
+          <t>188567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1620</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6027</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>71079</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67655</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>73025</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>80608</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76471</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76158</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,03%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>71079</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>67640</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>73004</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>146800</t>
+          <t>147402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153972</t>
+          <t>154303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>25690</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>8630</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14748</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15113</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>6218</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11033</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>336681</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>331616</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>340033</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>327975</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>321857</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>332113</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>321492</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>331942</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>336681</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>331866</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>340072</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>657123</t>
+          <t>657424</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>670298</t>
+          <t>670002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1563</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5247</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5013</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4917</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6105,74 +6105,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48951</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45707</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43019</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48951</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>131</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88616</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6340,67 +6340,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4759</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6361</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52663</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49271</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53945</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49373</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>55734</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>52663</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49717</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101668</t>
+          <t>101997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109013</t>
+          <t>108694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,107 +6678,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>729</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -6791,74 +6791,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27910</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27071</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>31125</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>93</t>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61775</t>
+          <t>61809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3441</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7637</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8445</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1609</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5441</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>102256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98653</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>107659</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>103463</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102655</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>109761</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>102256</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>98424</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205220</t>
+          <t>204991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212969</t>
+          <t>212960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2581</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7091</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4266</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>8281</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>5,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3431</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7333</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -7482,102 +7482,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>72735</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68528</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>66582</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62072</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>68504</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>62817</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>68507</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,05%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72735</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>69319</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>139317</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>134467</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>141455</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>94,2%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>139317</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>135415</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>141890</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>32601</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10666</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>8540</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4770</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14824</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14913</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>5388</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2208</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>10268</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>343093</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>337815</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>346028</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>334203</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>327919</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>337973</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>327830</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>338145</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,51%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,67%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>343093</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>338213</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>346273</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>669163</t>
+          <t>670466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>682761</t>
+          <t>682463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>497</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
